--- a/dados/contratos.xlsx
+++ b/dados/contratos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\27120642839\Documents\Aluguel\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB9BA25-DF65-47E5-87F8-93FC6CCD41CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E36BF048-407A-47DA-9D47-76855A8C45AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -499,6 +499,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="11.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -531,7 +535,7 @@
         <v>1200</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -551,13 +555,13 @@
         <v>1500</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -571,13 +575,13 @@
         <v>900</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -591,7 +595,7 @@
         <v>2000</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E5">
         <v>4</v>
@@ -611,13 +615,13 @@
         <v>1800</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -631,13 +635,13 @@
         <v>1300</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -651,7 +655,7 @@
         <v>2200</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="E8">
         <v>3</v>
@@ -671,13 +675,13 @@
         <v>1600</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E9">
         <v>4</v>
       </c>
       <c r="F9">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -691,13 +695,13 @@
         <v>1400</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -711,13 +715,13 @@
         <v>1700</v>
       </c>
       <c r="D11">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E11">
         <v>1</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -731,13 +735,13 @@
         <v>1250</v>
       </c>
       <c r="D12">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -751,13 +755,13 @@
         <v>1550</v>
       </c>
       <c r="D13">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -771,13 +775,13 @@
         <v>950</v>
       </c>
       <c r="D14">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="E14">
         <v>3</v>
       </c>
       <c r="F14">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -791,13 +795,13 @@
         <v>2100</v>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="E15">
         <v>4</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -811,13 +815,13 @@
         <v>1750</v>
       </c>
       <c r="D16">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F16">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -831,13 +835,13 @@
         <v>1350</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F17">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -851,13 +855,13 @@
         <v>2250</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="E18">
         <v>3</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -871,7 +875,7 @@
         <v>1650</v>
       </c>
       <c r="D19">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="E19">
         <v>4</v>
@@ -891,13 +895,13 @@
         <v>1450</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="E20">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F20">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -911,13 +915,13 @@
         <v>1850</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F21">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
